--- a/Finding restriction site.xlsx
+++ b/Finding restriction site.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gshao\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C65D89-BF08-46BE-B6E9-D2838595E247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B686745D-0020-4694-B690-CB7DC18C5CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" xr2:uid="{6DDB42B0-89A2-4E2C-BA91-5E03B392527E}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>BsaI</t>
   </si>
@@ -156,13 +156,19 @@
   </si>
   <si>
     <t>Reverse complementary sequence</t>
+  </si>
+  <si>
+    <t>←</t>
+  </si>
+  <si>
+    <t>→</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,6 +184,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -357,9 +380,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -381,6 +405,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -721,107 +749,108 @@
     <col min="2" max="2" width="21.7265625" customWidth="1"/>
     <col min="3" max="3" width="17.453125" customWidth="1"/>
     <col min="4" max="4" width="14.7265625" customWidth="1"/>
+    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B3" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B4" s="2" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B5" s="2" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="3" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B8" s="6" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B9" s="8" t="s">
+    <row r="9" spans="1:11" ht="21" x14ac:dyDescent="0.5">
+      <c r="B9" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E9" t="s">
@@ -830,50 +859,57 @@
       <c r="F9" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
+      <c r="G9" s="2"/>
+      <c r="H9" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B10" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B11" s="8" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="10" t="s">
+    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="12" t="s">
+    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="21" x14ac:dyDescent="0.5">
+      <c r="A16" s="21" t="s">
+        <v>29</v>
+      </c>
       <c r="B16" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>10</v>
       </c>
     </row>
@@ -885,7 +921,7 @@
     </row>
     <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="14" t="s">
         <v>9</v>
       </c>
     </row>
@@ -900,7 +936,7 @@
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -915,7 +951,7 @@
       <c r="A27" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="14" t="s">
         <v>27</v>
       </c>
     </row>
@@ -927,102 +963,102 @@
     </row>
     <row r="29" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:4" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="3">
         <f>FIND(F9,B22)</f>
         <v>990</v>
       </c>
-      <c r="D31" s="9" t="str">
+      <c r="D31" s="10" t="str">
         <f>MID(B22,C31,11)</f>
         <v>GGTCTCAATGG</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="2" t="e">
+      <c r="C32" s="3" t="e">
         <f>FIND(F9,B22,C31+1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D32" s="9" t="e">
+      <c r="D32" s="10" t="e">
         <f>MID(B22,C32,11)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="3" t="e">
+      <c r="C33" s="4" t="e">
         <f>FIND(F9,B22,C32+2)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D33" s="11" t="e">
+      <c r="D33" s="12" t="e">
         <f>MID(B22,C33,11)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="35" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="36" spans="2:4" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="19" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="3">
         <f>FIND(F9,B28)</f>
         <v>2908</v>
       </c>
-      <c r="D37" s="9" t="str">
+      <c r="D37" s="10" t="str">
         <f>MID(B28,C37,11)</f>
         <v>GGTCTCAAGCC</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C38" s="2" t="e">
+      <c r="C38" s="3" t="e">
         <f>FIND(F9,B28,C37+1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D38" s="9" t="e">
+      <c r="D38" s="10" t="e">
         <f>MID(B28,C38,11)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="39" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="3" t="e">
+      <c r="C39" s="4" t="e">
         <f>FIND(F9,B28,C38+1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D39" s="11" t="e">
+      <c r="D39" s="12" t="e">
         <f>MID(B28,C39,11)</f>
         <v>#VALUE!</v>
       </c>

--- a/Finding restriction site.xlsx
+++ b/Finding restriction site.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gshao\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B686745D-0020-4694-B690-CB7DC18C5CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF20C63F-03FF-42BC-B0F1-2AA7FF304540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" xr2:uid="{6DDB42B0-89A2-4E2C-BA91-5E03B392527E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6DDB42B0-89A2-4E2C-BA91-5E03B392527E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="7" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
   <si>
     <t>BsaI</t>
   </si>
@@ -162,6 +162,9 @@
   </si>
   <si>
     <t>→</t>
+  </si>
+  <si>
+    <t>length</t>
   </si>
 </sst>
 </file>
@@ -380,13 +383,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -408,6 +409,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -753,93 +757,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
@@ -847,10 +815,10 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="21" x14ac:dyDescent="0.5">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>5</v>
       </c>
       <c r="E9" t="s">
@@ -860,37 +828,37 @@
         <v>1</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="18" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>8</v>
       </c>
     </row>
@@ -900,7 +868,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="21" x14ac:dyDescent="0.5">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="19" t="s">
         <v>29</v>
       </c>
       <c r="B16" t="s">
@@ -909,7 +877,7 @@
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="12" t="s">
         <v>10</v>
       </c>
     </row>
@@ -921,8 +889,15 @@
     </row>
     <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="12" t="s">
         <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21">
+        <f>LEN(B22)</f>
+        <v>3938</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -936,8 +911,15 @@
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="12" t="s">
         <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24">
+        <f>LEN(B25)</f>
+        <v>3938</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -947,12 +929,19 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="20" t="s">
         <v>27</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27">
+        <f>LEN(B28)</f>
+        <v>3938</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -963,102 +952,102 @@
     </row>
     <row r="29" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:4" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31">
         <f>FIND(F9,B22)</f>
         <v>990</v>
       </c>
-      <c r="D31" s="10" t="str">
+      <c r="D31" s="8" t="str">
         <f>MID(B22,C31,11)</f>
         <v>GGTCTCAATGG</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="3" t="e">
+      <c r="C32" t="e">
         <f>FIND(F9,B22,C31+1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D32" s="10" t="e">
+      <c r="D32" s="8" t="e">
         <f>MID(B22,C32,11)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="4" t="e">
+      <c r="C33" s="3" t="e">
         <f>FIND(F9,B22,C32+2)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D33" s="12" t="e">
+      <c r="D33" s="10" t="e">
         <f>MID(B22,C33,11)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="35" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="36" spans="2:4" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="17" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37">
         <f>FIND(F9,B28)</f>
         <v>2908</v>
       </c>
-      <c r="D37" s="10" t="str">
+      <c r="D37" s="8" t="str">
         <f>MID(B28,C37,11)</f>
         <v>GGTCTCAAGCC</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C38" s="3" t="e">
+      <c r="C38" t="e">
         <f>FIND(F9,B28,C37+1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D38" s="10" t="e">
+      <c r="D38" s="8" t="e">
         <f>MID(B28,C38,11)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="39" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="4" t="e">
+      <c r="C39" s="3" t="e">
         <f>FIND(F9,B28,C38+1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D39" s="12" t="e">
+      <c r="D39" s="10" t="e">
         <f>MID(B28,C39,11)</f>
         <v>#VALUE!</v>
       </c>

--- a/Finding restriction site.xlsx
+++ b/Finding restriction site.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gshao\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF20C63F-03FF-42BC-B0F1-2AA7FF304540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2A07B5-CF92-4C64-BEAB-50AB6C339CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6DDB42B0-89A2-4E2C-BA91-5E03B392527E}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="7" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Anti">Sheet1!$C$9:$C$12</definedName>
+    <definedName name="Anti">Sheet1!$C$13:$C$16</definedName>
     <definedName name="aX">#REF!</definedName>
     <definedName name="aY">#REF!</definedName>
     <definedName name="bX">#REF!</definedName>
     <definedName name="bY">#REF!</definedName>
     <definedName name="cX">#REF!</definedName>
     <definedName name="cY">#REF!</definedName>
-    <definedName name="Sense">Sheet1!$B$9:$B$12</definedName>
+    <definedName name="Sense">Sheet1!$B$13:$B$16</definedName>
     <definedName name="tX">#REF!</definedName>
     <definedName name="tY">#REF!</definedName>
     <definedName name="X">#REF!</definedName>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>BsaI</t>
   </si>
@@ -165,6 +165,21 @@
   </si>
   <si>
     <t>length</t>
+  </si>
+  <si>
+    <t>References:</t>
+  </si>
+  <si>
+    <t>Addgene MoClo kit</t>
+  </si>
+  <si>
+    <t>https://www.addgene.org/cloning/moclo/</t>
+  </si>
+  <si>
+    <t>https://www.addgene.org/kits/wittbrodt-golden-gateway/#:~:text=In%20preparation%20for%20using%20the,in%20the%20final%20expression%20vector.</t>
+  </si>
+  <si>
+    <t>Golden Gateway kit Kit #1000000054</t>
   </si>
 </sst>
 </file>
@@ -383,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -411,6 +426,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -747,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5985685-000E-4298-8D05-DCA05A6DB060}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.7265625" customWidth="1"/>
@@ -756,7 +777,7 @@
     <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -768,27 +789,27 @@
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
@@ -802,253 +823,331 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B8" s="5" t="s">
+    <row r="7" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B8" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B9" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+    </row>
+    <row r="10" spans="2:16" ht="29" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="21" x14ac:dyDescent="0.5">
-      <c r="B9" s="7" t="s">
+    <row r="13" spans="2:16" ht="21" x14ac:dyDescent="0.5">
+      <c r="B13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E13" t="s">
         <v>0</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="18" t="s">
+      <c r="G13" s="2"/>
+      <c r="H13" s="18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B10" s="7" t="s">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B14" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C14" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B11" s="7" t="s">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B15" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C16" s="10" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="21" x14ac:dyDescent="0.5">
-      <c r="A16" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="21" x14ac:dyDescent="0.5">
+      <c r="A20" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B19">
-        <f>LEN(B16)</f>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B23">
+        <f>LEN(B20)</f>
         <v>3938</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="12" t="s">
+    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C25" t="s">
         <v>30</v>
       </c>
-      <c r="D21">
-        <f>LEN(B22)</f>
+      <c r="D25">
+        <f>LEN(B26)</f>
         <v>3938</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>11</v>
       </c>
-      <c r="B22" t="str">
-        <f>UPPER(B16)</f>
+      <c r="B26" t="str">
+        <f>UPPER(B20)</f>
         <v>AAATTGTAAACGTTAATATTTTGTTAAAATTCGCGTTAAATTTTTGTTAAATCAGCTCATTTTTTAACCAATAGGCCGAAATCGGCAAAATCCCTTATAAATCAAAAGAATAGACCGAGATAGGGTTGAGTGTTGTTCCAGTTTGGAACAAGAGTCCACTATTAAAGAACGTGGACTCCAACGTCAAAGGGCGAAAAACCGTCTATCAGGGCGATGGCCCACTACGTGAACCATCACCCTAATCAAGTTTTTTGGGGTCGAGGTGCCGTAAAGCACTAAATCGGAACCCTAAAGGGAGCCCCCGATTTAGAGCTTGACGGGGAAAGCCGGCGAACGTGGCGAGAAAGGAAGGGAAGAAAGCGAAAGGAGCGGGCGCTAGGGCGCTGGCAAGTGTAGCGGTCACGCTGCGCGTAACCACCACACCCGCCGCGCTTAATGCGCCGCTACAGGGCGCGTCCCATTCGCCATTCAGGCTACGCAACTGTTGGGAAGGGCGATCGGTGCGGGCCTCTTCGCTATTACGCCAGGGCGCCTCCCCCATTGACGTCAATTACGGTAAATGGCCCGCCTGGCTCAATGCCCATTGACGTCAATAGGACCACCCACCATTGACGTCAATGGGATGGCTCATTGCCCATTCATATCCGTTCTCACGCCCCCTATTGACGTCAATGACGGTAAATGGCCCACTTGGCAGTACATCAATATCTATTAATAGTAACTTGGCAAGTACATTACTATTGGAAGTACGCCAGGGTACATTGGCAGTACTCCCATTGACGTCAATGGCGGTAAATGGCCCGCGATGGCTGCCAAGTACATCCCCATTGACGTCAATGGGGAGGGGCAATGACGCAAATGGGCGTTCCATTGACGTAAATGGGCGGTAGGCGTGCCTAATGGGAGGTCTATATAAGCAATGCTCGTTTAGGGAACCGCCATTCTGCCTGGGGACGTCGGAGCAAGCTTGATTTAGGTGACACTATAGAGGTCTCAATGGGCGGATCCGGCGGCGGTACCGGCTTGAGACCCTCATCCTCCCGGGTAACTAAGTAAGGATCTCGACCGATCCTGAGAACTTCAGGGTGAGTTTGGGGACCCTTGATTGTTCTTTCTTTTTCGCTATTGTAAAATTCATGTTATATGGAGGGGGCAAAGTTTTCAGGGTGTTGTTTAGAATGGGAAGATGTCCCTTGTATCACCATGGACCCTCATGATAATTTTGTTTCTTTCACTTTCTACTCTGTTGACAACCATTGTCTCCTCTTATTTTCTTTTCATTTTCTGTAACTTTTTCGTTAAACTTTAGCTTGCATTTGTAACGAATTTTTAAATTCACTTTTGTTTATTTGTCAGATTGTAAGTACTTTCTCTAATCACTTTTTTTTCAAGGCAATCAGGGTATATTATATTGTACTTCAGCACAGTTTTAGAGAACAATTGTTATAATTAAATGATAAGGTAGAATATTTCTGCATATAAATTCTGGCTGGCGTGGAAATATTCTTATTGGTAGAAACAACTACACCCTGGTCATCATCCTGCCTTTCTCTTTATGGTTACAATGATATACACTGTTTGAGATGAGGATAAAATACTCTGAGTCCAAACCGGGCCCCTCTGCTAACCATGTTCATGCCTTCTTCTCTTTCCTACAGCTCCTGGGCAACGTGCTGGTTGTTGTGCTGTCTCATCATTTTGGCAAAGAATTAATTCCTCGACGGATCGTAGATCCAGACATGATAAGATACATTGATGAGTTTGGACAAACCACAACTAGAATGCAGTGAAAAAAATGCTTTATTTGTGAAATTTGTGATGCTATTGCTTTATTTGTAACCATTATAAGCTGCAATAAACAAGTTAACAACAACAATTGCATTCATTTTATGTTTCAGGTTCAGGGGGAGGTGTGGGAGGTTTTTTAATTCGCGGCCGCTCTAGAACTAGTCTGCATTAATGAATCGGCCAACGCGCGGGGAGAGGCGGTTTGCGTATTGGGCGCTCTTCCGCTTCCTCGCTCACTGACTCGCTGCGCTCGGTCGTTCGGCTGCGGCGAGCGGTATCAGCTCACTCAAAGGCGGTAATACGGTTATCCACAGAATCAGGGGATAACGCAGGAAAGAACATGTGAGCAAAAGGCCAGCAAAAGGCCAGGAACCGTAAAAAGGCCGCGTTGCTGGCGTTTTTCCATAGGCTCGGCCCCCCTGACGAGCATCACAAAAATCGACGCTCAAGTCAGAGGTGGCGAAACCCGACAGGACTATAAAGATACCAGGCGTTCCCCCCTGGAAGCTCCCTCGTGCGCTCTCCTGTTCCGACCCTGCCGCTTACCGGATACCTGTCCGCCTTTCTCCCTTCGGGAAGCGTGGCGCTTTCTCAATGCTCACGCTGTAGGTATCTCAGTTCGGTGTAGGTCGTTCGCTCCAAGCTGGGCTGTGTGCACGAACCCCCCGTTCAGCCCGACCGCTGCGCCTTATCCGGTAACTATCGTCTTGAGTCCAACCCGGTAAGACACGACTTATCGCCACTGGCAGCAGCCACTGGTAACAGGATTAGCAGAGCGAGGTATGTAGGCGGTGCTACAGAGTTCTTGAAGTGGTGGCCTAACTACGGCTACACTAGAAGGACAGTATTTGGTATCTGCGCTCTGCTGAAGCCAGTTACCTTCGGAAAAAGAGTTGGTAGCTCTTGATCCGGCAAACAAACCACCGCTGGTAGCGGTGGTTTTTTTGTTTGCAAGCAGCAGATTACGCGCAGAAAAAAAGGATCTCAAGAAGATCCTTTGATCTTTTCTACGGGGTCTGACGCTCAGTGGAACGAAAACTCACGTTAAGGGATTTTGGTCATGAGATTATCAAAAAGGATCTTCACCTAGATCCTTTTAAATTAAAAATGAAGTTTTAAATCAATCTAAAGTATATATGAGTAAACTTGGTCTGACAGTTACCAATGCTTAATCAGTGAGGCACCTATCTCAGCGATCTGTCTATTTCGTTCATCCATAGTTGCCTGACTGCCCGTCGTGTAGATAACTACGATACGGGAGGGCTTACCATCTGGCCCCAGTGCTGCAATGATACCGCGGGACCCACGCTCACCGGCTCCAGATTTATCAGCAATAAACCAGCCAGCCGGAAGGGCCGAGCGCAGAAGTGGTCCTGCAACTTTATCCGCCTCCATCCAGTCTATTAATTGTTGCCGGGAAGCTAGAGTAAGTAGTTCGCCAGTTAATAGTTTGCGCAACGTTGTTGCCATTGCTACAGGCATCGTGGTGTCACGCTCGTCGTTTGGTATGGCTTCATTCAGCTCCGGTTCCCAACGATCAAGGCGAGTTACATGATCCCCCATGTTGTGAAAAAAAGCGGTTAGCTCCTTCGGTCCTCCGATCGTTGTCAGAAGTAAGTTGGCCGCAGTGTTATCACTCATGCTTATGGCAGCACTGCATAATTCTCTTACTGTCATGCCATCCGTAAGATGCTTTTCTGTGACTGGTGAGTACTCAACCAAGTCATTCTGAGAATAGTGTATGCGGCGACCGAGTTGCTCTTGCCCGGCGTCAATACGGGATAATACCGCGCCACATAGCAGAACTTTAAAAGTGCTCATCATTGGAAAACGTTCTTCGGGGCGAAAACTCTCAAGGATCTTACCGCTGTTGAGATCCAGTTCGATGTAACCCACTCGTGCACCCAACTGATCTTCAGCATCTTTTACTTTCACCAGCGTTTCTGGGTGAGCAAAAACAGGAAGGCAAAATGCCGCAAAAAAGGGAATAAGGGCGACACGGAAATGTTGAATACTCATACTCTTCCTTTTTCAATATTATTGAAGCATTTATCAGGGTTATTGTCTCATGAGCGGATACATATTTGAATGTATTTAGAAAAATAAACAAATAGGGGTTCCGCGCACATTTCCCCGAAAAGTGCCACCTG</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="12" t="s">
+    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C28" t="s">
         <v>30</v>
       </c>
-      <c r="D24">
-        <f>LEN(B25)</f>
+      <c r="D28">
+        <f>LEN(B29)</f>
         <v>3938</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B25" t="str" cm="1">
-        <f t="array" ref="B25">_xlfn.TEXTJOIN(,TRUE,MID(B22,_xlfn.SEQUENCE(B19, ,B19, -1),1))</f>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B29" t="str" cm="1">
+        <f t="array" ref="B29">_xlfn.TEXTJOIN(,TRUE,MID(B26,_xlfn.SEQUENCE(B23, ,B23, -1),1))</f>
         <v>GTCCACCGTGAAAAGCCCCTTTACACGCGCCTTGGGGATAAACAAATAAAAAGATTTATGTAAGTTTATACATAGGCGAGTACTCTGTTATTGGGACTATTTACGAAGTTATTATAACTTTTTCCTTCTCATACTCATAAGTTGTAAAGGCACAGCGGGAATAAGGGAAAAAACGCCGTAAAACGGAAGGACAAAAACGAGTGGGTCTTTGCGACCACTTTCATTTTCTACGACTTCTAGTCAACCCACGTGCTCACCCAATGTAGCTTGACCTAGAGTTGTCGCCATTCTAGGAACTCTCAAAAGCGGGGCTTCTTGCAAAAGGTTACTACTCGTGAAAATTTCAAGACGATACACCGCGCCATAATAGGGCATAACTGCGGCCCGTTCTCGTTGAGCCAGCGGCGTATGTGATAAGAGTCTTACTGAACCAACTCATGAGTGGTCAGTGTCTTTTCGTAGAATGCCTACCGTACTGTCATTCTCTTAATACGTCACGACGGTATTCGTACTCACTATTGTGACGCCGGTTGAATGAAGACTGTTGCTAGCCTCCTGGCTTCCTCGATTGGCGAAAAAAAGTGTTGTACCCCCTAGTACATTGAGCGGAACTAGCAACCCTTGGCCTCGACTTACTTCGGTATGGTTTGCTGCTCGCACTGTGGTGCTACGGACATCGTTACCGTTGTTGCAACGCGTTTGATAATTGACCGCTTGATGAATGAGATCGAAGGGCCGTTGTTAATTATCTGACCTACCTCCGCCTATTTCAACGTCCTGGTGAAGACGCGAGCCGGGAAGGCCGACCGACCAAATAACGACTATTTAGACCTCGGCCACTCGCACCCAGGGCGCCATAGTAACGTCGTGACCCCGGTCTACCATTCGGGAGGGCATAGCATCAATAGATGTGCTGCCCGTCAGTCCGTTGATACCTACTTGCTTTATCTGTCTAGCGACTCTATCCACGGAGTGACTAATTCGTAACCATTGACAGTCTGGTTCAAATGAGTATATATGAAATCTAACTAAATTTTGAAGTAAAAATTAAATTTTCCTAGATCCACTTCTAGGAAAAACTATTAGAGTACTGGTTTTAGGGAATTGCACTCAAAAGCAAGGTGACTCGCAGTCTGGGGCATCTTTTCTAGTTTCCTAGAAGAACTCTAGGAAAAAAAGACGCGCATTAGACGACGAACGTTTGTTTTTTTGGTGGCGATGGTCGCCACCAAACAAACGGCCTAGTTCTCGATGGTTGAGAAAAAGGCTTCCATTGACCGAAGTCGTCTCGCGTCTATGGTTTATGACAGGAAGATCACATCGGCATCAATCCGGTGGTGAAGTTCTTGAGACATCGTGGCGGATGTATGGAGCGAGACGATTAGGACAATGGTCACCGACGACGGTCACCGCTATTCAGCACAGAATGGCCCAACCTGAGTTCTGCTATCAATGGCCTATTCCGCGTCGCCAGCCCGACTTGCCCCCCAAGCACGTGTGTCGGGTCGAACCTCGCTTGCTGGATGTGGCTTGACTCTATGGATGTCGCACTCGTAACTCTTTCGCGGTGCGAAGGGCTTCCCTCTTTCCGCCTGTCCATAGGCCATTCGCCGTCCCAGCCTTGTCCTCTCGCGTGCTCCCTCGAAGGTCCCCCCTTGCGGACCATAGAAATATCAGGACAGCCCAAAGCGGTGGAGACTGAACTCGCAGCTAAAAACACTACGAGCAGTCCCCCCGGCTCGGATACCTTTTTGCGGTCGTTGCGCCGGAAAAATGCCAAGGACCGGAAAACGACCGGAAAACGAGTGTACAAGAAAGGACGCAATAGGGGACTAAGACACCTATTGGCATAATGGCGGAAACTCACTCGACTATGGCGAGCGGCGTCGGCTTGCTGGCTCGCGTCGCTCAGTCACTCGCTCCTTCGCCTTCTCGCGGGTTATGCGTTTGGCGGAGAGGGGCGCGCAACCGGCTAAGTAATTACGTCTGATCAAGATCTCGCCGGCGCTTAATTTTTTGGAGGGTGTGGAGGGGGACTTGGACTTTGTATTTTACTTACGTTAACAACAACAATTGAACAAATAACGTCGAATATTACCAATGTTTATTTCGTTATCGTAGTGTTTAAAGTGTTTATTTCGTAAAAAAAGTGACGTAAGATCAACACCAAACAGGTTTGAGTAGTTACATAGAATAGTACAGACCTAGATGCTAGGCAGCTCCTTAATTAAGAAACGGTTTTACTACTCTGTCGTGTTGTTGGTCGTGCAACGGGTCCTCGACATCCTTTCTCTTCTTCCGTACTTGTACCAATCGTCTCCCCGGGCCAAACCTGAGTCTCATAAAATAGGAGTAGAGTTTGTCACATATAGTAACATTGGTATTTCTCTTTCCGTCCTACTACTGGTCCCACATCAACAAAGATGGTTATTCTTATAAAGGTGCGGTCGGTCTTAAATATACGTCTTTATAAGATGGAATAGTAAATTAATATTGTTAACAAGAGATTTTGACACGACTTCATGTTATATTATATGGGACTAACGGAACTTTTTTTTCACTAATCTCTTTCATGAATGTTAGACTGTTTATTTGTTTTCACTTAAATTTTTAAGCAATGTTTACGTTCGATTTCAAATTGCTTTTTCAATGTCTTTTACTTTTCTTTTATTCTCCTCTGTTACCAACAGTTGTCTCATCTTTCACTTTCTTTGTTTTAATAGTACTCCCAGGTACCACTATGTTCCCTGTAGAAGGGTAAGATTTGTTGTGGGACTTTTGAAACGGGGGAGGTATATTGTACTTAAAATGTTATCGCTTTTTCTTTCTTGTTAGTTCCCAGGGGTTTGAGTGGGACTTCAAGAGTCCTAGCCAGCTCTAGGAATGAATCAATGGGCCCTCCTACTCCCAGAGTTCGGCCATGGCGGCGGCCTAGGCGGGTAACTCTGGAGATATCACAGTGGATTTAGTTCGAACGAGGCTGCAGGGGTCCGTCTTACCGCCAAGGGATTTGCTCGTAACGAATATATCTGGAGGGTAATCCGTGCGGATGGCGGGTAAATGCAGTTACCTTGCGGGTAAACGCAGTAACGGGGAGGGGTAACTGCAGTTACCCCTACATGAACCGTCGGTAGCGCCCGGTAAATGGCGGTAACTGCAGTTACCCTCATGACGGTTACATGGGACCGCATGAAGGTTATCATTACATGAACGGTTCAATGATAATTATCTATAACTACATGACGGTTCACCCGGTAAATGGCAGTAACTGCAGTTATCCCCCGCACTCTTGCCTATACTTACCCGTTACTCGGTAGGGTAACTGCAGTTACCACCCACCAGGATAACTGCAGTTACCCGTAACTCGGTCCGCCCGGTAAATGGCATTAACTGCAGTTACCCCCTCCGCGGGACCGCATTATCGCTTCTCCGGGCGTGGCTAGCGGGAAGGGTTGTCAACGCATCGGACTTACCGCTTACCCTGCGCGGGACATCGCCGCGTAATTCGCGCCGCCCACACCACCAATGCGCGTCGCACTGGCGATGTGAACGGTCGCGGGATCGCGGGCGAGGAAAGCGAAAGAAGGGAAGGAAAGAGCGGTGCAAGCGGCCGAAAGGGGCAGTTCGAGATTTAGCCCCCGAGGGAAATCCCAAGGCTAAATCACGAAATGCCGTGGAGCTGGGGTTTTTTGAACTAATCCCACTACCAAGTGCATCACCCGGTAGCGGGACTATCTGCCAAAAAGCGGGAAACTGCAACCTCAGGTGCAAGAAATTATCACCTGAGAACAAGGTTTGACCTTGTTGTGAGTTGGGATAGAGCCAGATAAGAAAACTAAATATTCCCTAAAACGGCTAAAGCCGGATAACCAATTTTTTACTCGACTAAATTGTTTTTAAATTGCGCTTAAAATTGTTTTATAATTGCAAATGTTAAA</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="27" spans="1:4" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
+    <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="31" spans="1:4" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B31" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C31" t="s">
         <v>30</v>
       </c>
-      <c r="D27">
-        <f>LEN(B28)</f>
+      <c r="D31">
+        <f>LEN(B32)</f>
         <v>3938</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B28" t="str" cm="1">
-        <f t="array" ref="B28">_xlfn.TEXTJOIN(,TRUE,_xlfn.XLOOKUP(MID(B22,_xlfn.SEQUENCE(B19, ,B19, -1),1),Sense,Anti))</f>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B32" t="str" cm="1">
+        <f t="array" ref="B32">_xlfn.TEXTJOIN(,TRUE,_xlfn.XLOOKUP(MID(B26,_xlfn.SEQUENCE(B23, ,B23, -1),1),Sense,Anti))</f>
         <v>CAGGTGGCACTTTTCGGGGAAATGTGCGCGGAACCCCTATTTGTTTATTTTTCTAAATACATTCAAATATGTATCCGCTCATGAGACAATAACCCTGATAAATGCTTCAATAATATTGAAAAAGGAAGAGTATGAGTATTCAACATTTCCGTGTCGCCCTTATTCCCTTTTTTGCGGCATTTTGCCTTCCTGTTTTTGCTCACCCAGAAACGCTGGTGAAAGTAAAAGATGCTGAAGATCAGTTGGGTGCACGAGTGGGTTACATCGAACTGGATCTCAACAGCGGTAAGATCCTTGAGAGTTTTCGCCCCGAAGAACGTTTTCCAATGATGAGCACTTTTAAAGTTCTGCTATGTGGCGCGGTATTATCCCGTATTGACGCCGGGCAAGAGCAACTCGGTCGCCGCATACACTATTCTCAGAATGACTTGGTTGAGTACTCACCAGTCACAGAAAAGCATCTTACGGATGGCATGACAGTAAGAGAATTATGCAGTGCTGCCATAAGCATGAGTGATAACACTGCGGCCAACTTACTTCTGACAACGATCGGAGGACCGAAGGAGCTAACCGCTTTTTTTCACAACATGGGGGATCATGTAACTCGCCTTGATCGTTGGGAACCGGAGCTGAATGAAGCCATACCAAACGACGAGCGTGACACCACGATGCCTGTAGCAATGGCAACAACGTTGCGCAAACTATTAACTGGCGAACTACTTACTCTAGCTTCCCGGCAACAATTAATAGACTGGATGGAGGCGGATAAAGTTGCAGGACCACTTCTGCGCTCGGCCCTTCCGGCTGGCTGGTTTATTGCTGATAAATCTGGAGCCGGTGAGCGTGGGTCCCGCGGTATCATTGCAGCACTGGGGCCAGATGGTAAGCCCTCCCGTATCGTAGTTATCTACACGACGGGCAGTCAGGCAACTATGGATGAACGAAATAGACAGATCGCTGAGATAGGTGCCTCACTGATTAAGCATTGGTAACTGTCAGACCAAGTTTACTCATATATACTTTAGATTGATTTAAAACTTCATTTTTAATTTAAAAGGATCTAGGTGAAGATCCTTTTTGATAATCTCATGACCAAAATCCCTTAACGTGAGTTTTCGTTCCACTGAGCGTCAGACCCCGTAGAAAAGATCAAAGGATCTTCTTGAGATCCTTTTTTTCTGCGCGTAATCTGCTGCTTGCAAACAAAAAAACCACCGCTACCAGCGGTGGTTTGTTTGCCGGATCAAGAGCTACCAACTCTTTTTCCGAAGGTAACTGGCTTCAGCAGAGCGCAGATACCAAATACTGTCCTTCTAGTGTAGCCGTAGTTAGGCCACCACTTCAAGAACTCTGTAGCACCGCCTACATACCTCGCTCTGCTAATCCTGTTACCAGTGGCTGCTGCCAGTGGCGATAAGTCGTGTCTTACCGGGTTGGACTCAAGACGATAGTTACCGGATAAGGCGCAGCGGTCGGGCTGAACGGGGGGTTCGTGCACACAGCCCAGCTTGGAGCGAACGACCTACACCGAACTGAGATACCTACAGCGTGAGCATTGAGAAAGCGCCACGCTTCCCGAAGGGAGAAAGGCGGACAGGTATCCGGTAAGCGGCAGGGTCGGAACAGGAGAGCGCACGAGGGAGCTTCCAGGGGGGAACGCCTGGTATCTTTATAGTCCTGTCGGGTTTCGCCACCTCTGACTTGAGCGTCGATTTTTGTGATGCTCGTCAGGGGGGCCGAGCCTATGGAAAAACGCCAGCAACGCGGCCTTTTTACGGTTCCTGGCCTTTTGCTGGCCTTTTGCTCACATGTTCTTTCCTGCGTTATCCCCTGATTCTGTGGATAACCGTATTACCGCCTTTGAGTGAGCTGATACCGCTCGCCGCAGCCGAACGACCGAGCGCAGCGAGTCAGTGAGCGAGGAAGCGGAAGAGCGCCCAATACGCAAACCGCCTCTCCCCGCGCGTTGGCCGATTCATTAATGCAGACTAGTTCTAGAGCGGCCGCGAATTAAAAAACCTCCCACACCTCCCCCTGAACCTGAAACATAAAATGAATGCAATTGTTGTTGTTAACTTGTTTATTGCAGCTTATAATGGTTACAAATAAAGCAATAGCATCACAAATTTCACAAATAAAGCATTTTTTTCACTGCATTCTAGTTGTGGTTTGTCCAAACTCATCAATGTATCTTATCATGTCTGGATCTACGATCCGTCGAGGAATTAATTCTTTGCCAAAATGATGAGACAGCACAACAACCAGCACGTTGCCCAGGAGCTGTAGGAAAGAGAAGAAGGCATGAACATGGTTAGCAGAGGGGCCCGGTTTGGACTCAGAGTATTTTATCCTCATCTCAAACAGTGTATATCATTGTAACCATAAAGAGAAAGGCAGGATGATGACCAGGGTGTAGTTGTTTCTACCAATAAGAATATTTCCACGCCAGCCAGAATTTATATGCAGAAATATTCTACCTTATCATTTAATTATAACAATTGTTCTCTAAAACTGTGCTGAAGTACAATATAATATACCCTGATTGCCTTGAAAAAAAAGTGATTAGAGAAAGTACTTACAATCTGACAAATAAACAAAAGTGAATTTAAAAATTCGTTACAAATGCAAGCTAAAGTTTAACGAAAAAGTTACAGAAAATGAAAAGAAAATAAGAGGAGACAATGGTTGTCAACAGAGTAGAAAGTGAAAGAAACAAAATTATCATGAGGGTCCATGGTGATACAAGGGACATCTTCCCATTCTAAACAACACCCTGAAAACTTTGCCCCCTCCATATAACATGAATTTTACAATAGCGAAAAAGAAAGAACAATCAAGGGTCCCCAAACTCACCCTGAAGTTCTCAGGATCGGTCGAGATCCTTACTTAGTTACCCGGGAGGATGAGGGTCTCAAGCCGGTACCGCCGCCGGATCCGCCCATTGAGACCTCTATAGTGTCACCTAAATCAAGCTTGCTCCGACGTCCCCAGGCAGAATGGCGGTTCCCTAAACGAGCATTGCTTATATAGACCTCCCATTAGGCACGCCTACCGCCCATTTACGTCAATGGAACGCCCATTTGCGTCATTGCCCCTCCCCATTGACGTCAATGGGGATGTACTTGGCAGCCATCGCGGGCCATTTACCGCCATTGACGTCAATGGGAGTACTGCCAATGTACCCTGGCGTACTTCCAATAGTAATGTACTTGCCAAGTTACTATTAATAGATATTGATGTACTGCCAAGTGGGCCATTTACCGTCATTGACGTCAATAGGGGGCGTGAGAACGGATATGAATGGGCAATGAGCCATCCCATTGACGTCAATGGTGGGTGGTCCTATTGACGTCAATGGGCATTGAGCCAGGCGGGCCATTTACCGTAATTGACGTCAATGGGGGAGGCGCCCTGGCGTAATAGCGAAGAGGCCCGCACCGATCGCCCTTCCCAACAGTTGCGTAGCCTGAATGGCGAATGGGACGCGCCCTGTAGCGGCGCATTAAGCGCGGCGGGTGTGGTGGTTACGCGCAGCGTGACCGCTACACTTGCCAGCGCCCTAGCGCCCGCTCCTTTCGCTTTCTTCCCTTCCTTTCTCGCCACGTTCGCCGGCTTTCCCCGTCAAGCTCTAAATCGGGGGCTCCCTTTAGGGTTCCGATTTAGTGCTTTACGGCACCTCGACCCCAAAAAACTTGATTAGGGTGATGGTTCACGTAGTGGGCCATCGCCCTGATAGACGGTTTTTCGCCCTTTGACGTTGGAGTCCACGTTCTTTAATAGTGGACTCTTGTTCCAAACTGGAACAACACTCAACCCTATCTCGGTCTATTCTTTTGATTTATAAGGGATTTTGCCGATTTCGGCCTATTGGTTAAAAAATGAGCTGATTTAACAAAAATTTAACGCGAATTTTAACAAAATATTAACGTTTACAATTT</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="30" spans="1:4" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="13" t="s">
+    <row r="33" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="34" spans="2:4" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C34" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D34" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B31" s="7" t="s">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B35" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C31">
-        <f>FIND(F9,B22)</f>
+      <c r="C35">
+        <f>FIND(F13,B26)</f>
         <v>990</v>
       </c>
-      <c r="D31" s="8" t="str">
-        <f>MID(B22,C31,11)</f>
+      <c r="D35" s="8" t="str">
+        <f>MID(B26,C35,11)</f>
         <v>GGTCTCAATGG</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B32" s="7" t="s">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B36" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C32" t="e">
-        <f>FIND(F9,B22,C31+1)</f>
+      <c r="C36" t="e">
+        <f>FIND(F13,B26,C35+1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D32" s="8" t="e">
-        <f>MID(B22,C32,11)</f>
+      <c r="D36" s="8" t="e">
+        <f>MID(B26,C36,11)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="9" t="s">
+    <row r="37" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B37" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="3" t="e">
-        <f>FIND(F9,B22,C32+2)</f>
+      <c r="C37" s="3" t="e">
+        <f>FIND(F13,B26,C36+2)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D33" s="10" t="e">
-        <f>MID(B22,C33,11)</f>
+      <c r="D37" s="10" t="e">
+        <f>MID(B26,C37,11)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="36" spans="2:4" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="15" t="s">
+    <row r="39" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="40" spans="2:4" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C40" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D40" s="17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B37" s="7" t="s">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C37">
-        <f>FIND(F9,B28)</f>
+      <c r="C41">
+        <f>FIND(F13,B32)</f>
         <v>2908</v>
       </c>
-      <c r="D37" s="8" t="str">
-        <f>MID(B28,C37,11)</f>
+      <c r="D41" s="8" t="str">
+        <f>MID(B32,C41,11)</f>
         <v>GGTCTCAAGCC</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B38" s="7" t="s">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C38" t="e">
-        <f>FIND(F9,B28,C37+1)</f>
+      <c r="C42" t="e">
+        <f>FIND(F13,B32,C41+1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D38" s="8" t="e">
-        <f>MID(B28,C38,11)</f>
+      <c r="D42" s="8" t="e">
+        <f>MID(B32,C42,11)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="9" t="s">
+    <row r="43" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B43" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="3" t="e">
-        <f>FIND(F9,B28,C38+1)</f>
+      <c r="C43" s="3" t="e">
+        <f>FIND(F13,B32,C42+1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D39" s="10" t="e">
-        <f>MID(B28,C39,11)</f>
+      <c r="D43" s="10" t="e">
+        <f>MID(B32,C43,11)</f>
         <v>#VALUE!</v>
       </c>
     </row>
